--- a/output/pdf_financials_xlsx/SLZ.xlsx
+++ b/output/pdf_financials_xlsx/SLZ.xlsx
@@ -1940,13 +1940,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.941198</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.941198</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.941198</v>
       </c>
     </row>
     <row r="93">
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.009794000000000001</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.024617</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.059473</v>
       </c>
     </row>
     <row r="119">
@@ -3050,7 +3050,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -3079,7 +3083,11 @@
           <t>Warrants reserve</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -3290,7 +3298,11 @@
           <t>Share-based payment reserve (Notes 6 and 8)</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>0.921198</v>
       </c>
@@ -3319,7 +3331,11 @@
           <t>Warrants reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>0.02</v>
       </c>
@@ -3526,7 +3542,11 @@
           <t>Exploration and evaluation asset expenditures</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>-0.009794000000000001</v>
       </c>

--- a/output/pdf_financials_xlsx/SLZ.xlsx
+++ b/output/pdf_financials_xlsx/SLZ.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.682401</v>
+        <v>0.842255</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.225761</v>
+        <v>0.267389</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.17051</v>
+        <v>0.209583</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.682401</v>
+        <v>-0.842255</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.225761</v>
+        <v>-0.267389</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.17051</v>
+        <v>-0.209583</v>
       </c>
     </row>
     <row r="12">
@@ -988,13 +988,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.084671</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.021063</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.020568</v>
       </c>
     </row>
     <row r="35">
@@ -1020,13 +1020,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.084671</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.021063</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.020568</v>
       </c>
     </row>
     <row r="37">
@@ -1212,13 +1212,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.131735</v>
+        <v>0.047064</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.023448</v>
+        <v>0.002385</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.059764</v>
+        <v>0.039196</v>
       </c>
     </row>
     <row r="49">
@@ -2709,7 +2709,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4607,7 +4607,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">

--- a/output/pdf_financials_xlsx/SLZ.xlsx
+++ b/output/pdf_financials_xlsx/SLZ.xlsx
@@ -2075,13 +2075,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.019789</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.054054</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.005927</v>
       </c>
     </row>
     <row r="102">
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.033079</v>
+        <v>-0.052868</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.056565</v>
+        <v>0.110619</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.0009700000000000001</v>
+        <v>0.006897</v>
       </c>
     </row>
     <row r="107">
@@ -3395,7 +3395,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
         <v>-0.019789</v>
       </c>
